--- a/outputs_xlsx_solution/test33.4-wide-NC-1.xlsx
+++ b/outputs_xlsx_solution/test33.4-wide-NC-1.xlsx
@@ -80,6 +80,9 @@
     <t>EX</t>
   </si>
   <si>
+    <t>FU Stall</t>
+  </si>
+  <si>
     <t>RS Stall</t>
   </si>
   <si>
@@ -207,6 +210,9 @@
   </si>
   <si>
     <t>Common Data Bus Stall (stalled because the CDB bandwidth is saturated)</t>
+  </si>
+  <si>
+    <t>Functional Unit Stall (stalled because the functional unit is busy)</t>
   </si>
 </sst>
 </file>
@@ -945,7 +951,7 @@
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3">
@@ -965,13 +971,13 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
         <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
@@ -991,16 +997,16 @@
         <v>9</v>
       </c>
       <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
-        <v>14</v>
-      </c>
       <c r="H4" t="s">
         <v>14</v>
       </c>
       <c r="I4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5">
@@ -1020,16 +1026,16 @@
         <v>9</v>
       </c>
       <c r="G5" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
       <c r="I5" t="s">
         <v>14</v>
       </c>
       <c r="J5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6">
@@ -1049,16 +1055,16 @@
         <v>9</v>
       </c>
       <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
         <v>15</v>
       </c>
-      <c r="I6" t="s">
-        <v>14</v>
-      </c>
       <c r="J6" t="s">
         <v>14</v>
       </c>
       <c r="K6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
@@ -1078,16 +1084,16 @@
         <v>9</v>
       </c>
       <c r="I7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" t="s">
         <v>15</v>
       </c>
-      <c r="J7" t="s">
-        <v>14</v>
-      </c>
       <c r="K7" t="s">
         <v>14</v>
       </c>
       <c r="L7" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -1110,10 +1116,10 @@
         <v>14</v>
       </c>
       <c r="K8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="M8" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -1133,16 +1139,16 @@
         <v>9</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K9" t="s">
         <v>14</v>
       </c>
       <c r="L9" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="N9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
@@ -1153,7 +1159,7 @@
         <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -1162,16 +1168,19 @@
         <v>9</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="K10" t="s">
+        <v>15</v>
       </c>
       <c r="L10" t="s">
         <v>14</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11">
@@ -1182,7 +1191,7 @@
         <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -1200,10 +1209,10 @@
         <v>14</v>
       </c>
       <c r="N11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
@@ -1214,7 +1223,7 @@
         <v>40</v>
       </c>
       <c r="C12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -1223,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="K12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N12" t="s">
         <v>14</v>
@@ -1235,7 +1244,7 @@
         <v>14</v>
       </c>
       <c r="Q12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -1246,7 +1255,7 @@
         <v>44</v>
       </c>
       <c r="C13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1255,7 +1264,16 @@
         <v>9</v>
       </c>
       <c r="K13" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>15</v>
+      </c>
+      <c r="R13" t="s">
+        <v>15</v>
+      </c>
+      <c r="S13" t="s">
+        <v>15</v>
       </c>
       <c r="T13" t="s">
         <v>14</v>
@@ -1270,7 +1288,7 @@
         <v>14</v>
       </c>
       <c r="X13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -1281,7 +1299,7 @@
         <v>48</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G14" t="s">
         <v>5</v>
@@ -1302,10 +1320,10 @@
         <v>14</v>
       </c>
       <c r="O14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15">
@@ -1316,7 +1334,7 @@
         <v>52</v>
       </c>
       <c r="C15" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G15" t="s">
         <v>5</v>
@@ -1343,10 +1361,10 @@
         <v>14</v>
       </c>
       <c r="R15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16">
@@ -1357,7 +1375,7 @@
         <v>56</v>
       </c>
       <c r="C16" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G16" t="s">
         <v>5</v>
@@ -1366,16 +1384,16 @@
         <v>9</v>
       </c>
       <c r="L16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M16" t="s">
         <v>14</v>
       </c>
       <c r="N16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AA16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -1395,16 +1413,19 @@
         <v>9</v>
       </c>
       <c r="L17" t="s">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="M17" t="s">
+        <v>15</v>
       </c>
       <c r="N17" t="s">
         <v>14</v>
       </c>
       <c r="O17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AB17" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="18">
@@ -1415,7 +1436,7 @@
         <v>64</v>
       </c>
       <c r="C18" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H18" t="s">
         <v>5</v>
@@ -1424,16 +1445,16 @@
         <v>9</v>
       </c>
       <c r="L18" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M18" t="s">
         <v>14</v>
       </c>
       <c r="N18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1444,7 +1465,7 @@
         <v>68</v>
       </c>
       <c r="C19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H19" t="s">
         <v>5</v>
@@ -1453,16 +1474,16 @@
         <v>9</v>
       </c>
       <c r="M19" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N19" t="s">
         <v>14</v>
       </c>
       <c r="O19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AD19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -1473,7 +1494,7 @@
         <v>72</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H20" t="s">
         <v>5</v>
@@ -1482,13 +1503,13 @@
         <v>9</v>
       </c>
       <c r="M20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P20" t="s">
         <v>14</v>
@@ -1503,10 +1524,10 @@
         <v>14</v>
       </c>
       <c r="T20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -1517,7 +1538,7 @@
         <v>76</v>
       </c>
       <c r="C21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H21" t="s">
         <v>5</v>
@@ -1526,7 +1547,7 @@
         <v>9</v>
       </c>
       <c r="O21" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="T21" t="s">
         <v>14</v>
@@ -1538,10 +1559,10 @@
         <v>14</v>
       </c>
       <c r="W21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
@@ -1552,7 +1573,7 @@
         <v>80</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I22" t="s">
         <v>5</v>
@@ -1561,16 +1582,16 @@
         <v>9</v>
       </c>
       <c r="O22" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="W22" t="s">
         <v>14</v>
       </c>
       <c r="X22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AG22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="23">
@@ -1581,7 +1602,7 @@
         <v>84</v>
       </c>
       <c r="C23" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I23" t="s">
         <v>5</v>
@@ -1590,16 +1611,16 @@
         <v>9</v>
       </c>
       <c r="O23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P23" t="s">
         <v>14</v>
       </c>
       <c r="Q23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH23" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24">
@@ -1610,7 +1631,7 @@
         <v>88</v>
       </c>
       <c r="C24" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I24" t="s">
         <v>5</v>
@@ -1619,16 +1640,16 @@
         <v>9</v>
       </c>
       <c r="P24" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Q24" t="s">
         <v>14</v>
       </c>
       <c r="R24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI24" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="25">
@@ -1639,7 +1660,7 @@
         <v>68</v>
       </c>
       <c r="C25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="R25" t="s">
         <v>5</v>
@@ -1648,16 +1669,16 @@
         <v>9</v>
       </c>
       <c r="T25" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="U25" t="s">
         <v>14</v>
       </c>
       <c r="V25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ25" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -1668,7 +1689,7 @@
         <v>72</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="R26" t="s">
         <v>5</v>
@@ -1677,7 +1698,13 @@
         <v>9</v>
       </c>
       <c r="T26" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="V26" t="s">
+        <v>15</v>
+      </c>
+      <c r="W26" t="s">
+        <v>15</v>
       </c>
       <c r="X26" t="s">
         <v>14</v>
@@ -1692,10 +1719,10 @@
         <v>14</v>
       </c>
       <c r="AB26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AK26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27">
@@ -1706,7 +1733,7 @@
         <v>76</v>
       </c>
       <c r="C27" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="R27" t="s">
         <v>5</v>
@@ -1715,7 +1742,7 @@
         <v>9</v>
       </c>
       <c r="T27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AB27" t="s">
         <v>14</v>
@@ -1727,10 +1754,10 @@
         <v>14</v>
       </c>
       <c r="AE27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL27" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28">
@@ -1741,7 +1768,7 @@
         <v>80</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R28" t="s">
         <v>5</v>
@@ -1750,16 +1777,16 @@
         <v>9</v>
       </c>
       <c r="T28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AE28" t="s">
         <v>14</v>
       </c>
       <c r="AF28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
@@ -1770,7 +1797,7 @@
         <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="S29" t="s">
         <v>5</v>
@@ -1779,25 +1806,25 @@
         <v>9</v>
       </c>
       <c r="U29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="V29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="W29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="X29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Y29" t="s">
         <v>14</v>
       </c>
       <c r="Z29" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AN29" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -1808,7 +1835,7 @@
         <v>88</v>
       </c>
       <c r="C30" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="S30" t="s">
         <v>5</v>
@@ -1817,19 +1844,19 @@
         <v>9</v>
       </c>
       <c r="X30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Y30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="Z30" t="s">
         <v>14</v>
       </c>
       <c r="AA30" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31">
@@ -1840,7 +1867,7 @@
         <v>68</v>
       </c>
       <c r="C31" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="T31" t="s">
         <v>5</v>
@@ -1849,19 +1876,19 @@
         <v>9</v>
       </c>
       <c r="Y31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="Z31" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AA31" t="s">
         <v>14</v>
       </c>
       <c r="AB31" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP31" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
@@ -1872,7 +1899,7 @@
         <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T32" t="s">
         <v>5</v>
@@ -1881,10 +1908,10 @@
         <v>9</v>
       </c>
       <c r="Z32" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AA32" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AB32" t="s">
         <v>14</v>
@@ -1899,10 +1926,10 @@
         <v>14</v>
       </c>
       <c r="AF32" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ32" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="33">
@@ -1913,7 +1940,7 @@
         <v>76</v>
       </c>
       <c r="C33" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="T33" t="s">
         <v>5</v>
@@ -1922,10 +1949,10 @@
         <v>9</v>
       </c>
       <c r="AA33" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AB33" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF33" t="s">
         <v>14</v>
@@ -1937,10 +1964,10 @@
         <v>14</v>
       </c>
       <c r="AI33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR33" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
@@ -1951,7 +1978,7 @@
         <v>80</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="T34" t="s">
         <v>5</v>
@@ -1960,19 +1987,19 @@
         <v>9</v>
       </c>
       <c r="AB34" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AC34" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AI34" t="s">
         <v>14</v>
       </c>
       <c r="AJ34" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AS34" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="35">
@@ -1983,7 +2010,7 @@
         <v>84</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="U35" t="s">
         <v>5</v>
@@ -1992,19 +2019,19 @@
         <v>9</v>
       </c>
       <c r="AC35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AD35" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AE35" t="s">
         <v>14</v>
       </c>
       <c r="AF35" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AT35" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="36">
@@ -2015,7 +2042,7 @@
         <v>88</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U36" t="s">
         <v>5</v>
@@ -2024,19 +2051,19 @@
         <v>9</v>
       </c>
       <c r="AD36" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AE36" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AF36" t="s">
         <v>14</v>
       </c>
       <c r="AG36" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU36" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="37">
@@ -2047,7 +2074,7 @@
         <v>92</v>
       </c>
       <c r="C37" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="AG37" t="s">
         <v>5</v>
@@ -2065,10 +2092,10 @@
         <v>14</v>
       </c>
       <c r="AL37" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV37" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="38">
@@ -2079,7 +2106,7 @@
         <v>96</v>
       </c>
       <c r="C38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="AG38" t="s">
         <v>5</v>
@@ -2088,7 +2115,7 @@
         <v>9</v>
       </c>
       <c r="AI38" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AL38" t="s">
         <v>14</v>
@@ -2100,10 +2127,10 @@
         <v>14</v>
       </c>
       <c r="AO38" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW38" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
@@ -2114,7 +2141,7 @@
         <v>100</v>
       </c>
       <c r="C39" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="AG39" t="s">
         <v>5</v>
@@ -2126,10 +2153,10 @@
         <v>14</v>
       </c>
       <c r="AJ39" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX39" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="40">
@@ -2140,7 +2167,7 @@
         <v>104</v>
       </c>
       <c r="C40" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="AG40" t="s">
         <v>5</v>
@@ -2149,10 +2176,10 @@
         <v>14</v>
       </c>
       <c r="AJ40" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AY40" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
@@ -2163,7 +2190,7 @@
         <v>36</v>
       </c>
       <c r="C41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH41" t="s">
         <v>5</v>
@@ -2181,10 +2208,10 @@
         <v>14</v>
       </c>
       <c r="AM41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ41" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="42">
@@ -2195,7 +2222,7 @@
         <v>40</v>
       </c>
       <c r="C42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AH42" t="s">
         <v>5</v>
@@ -2204,13 +2231,13 @@
         <v>9</v>
       </c>
       <c r="AJ42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL42" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AM42" t="s">
         <v>14</v>
@@ -2222,10 +2249,10 @@
         <v>14</v>
       </c>
       <c r="AP42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA42" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="43">
@@ -2236,7 +2263,7 @@
         <v>44</v>
       </c>
       <c r="C43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AH43" t="s">
         <v>5</v>
@@ -2245,7 +2272,10 @@
         <v>9</v>
       </c>
       <c r="AL43" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="AP43" t="s">
+        <v>15</v>
       </c>
       <c r="AQ43" t="s">
         <v>14</v>
@@ -2260,10 +2290,10 @@
         <v>14</v>
       </c>
       <c r="AU43" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BB43" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="44">
@@ -2274,7 +2304,7 @@
         <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH44" t="s">
         <v>5</v>
@@ -2283,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="AL44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AM44" t="s">
         <v>14</v>
@@ -2298,10 +2328,10 @@
         <v>14</v>
       </c>
       <c r="AQ44" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC44" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="45">
@@ -2312,7 +2342,7 @@
         <v>52</v>
       </c>
       <c r="C45" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI45" t="s">
         <v>5</v>
@@ -2321,7 +2351,7 @@
         <v>9</v>
       </c>
       <c r="AM45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AN45" t="s">
         <v>14</v>
@@ -2342,10 +2372,10 @@
         <v>14</v>
       </c>
       <c r="AT45" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD45" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="46">
@@ -2356,7 +2386,7 @@
         <v>56</v>
       </c>
       <c r="C46" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI46" t="s">
         <v>5</v>
@@ -2365,16 +2395,16 @@
         <v>9</v>
       </c>
       <c r="AN46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AO46" t="s">
         <v>14</v>
       </c>
       <c r="AP46" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BE46" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="47">
@@ -2394,16 +2424,16 @@
         <v>9</v>
       </c>
       <c r="AO47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AP47" t="s">
         <v>14</v>
       </c>
       <c r="AQ47" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BF47" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="48">
@@ -2414,7 +2444,7 @@
         <v>64</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI48" t="s">
         <v>5</v>
@@ -2423,19 +2453,19 @@
         <v>9</v>
       </c>
       <c r="AP48" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AQ48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AR48" t="s">
         <v>14</v>
       </c>
       <c r="AS48" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BG48" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="49">
@@ -2446,7 +2476,7 @@
         <v>68</v>
       </c>
       <c r="C49" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ49" t="s">
         <v>5</v>
@@ -2455,19 +2485,19 @@
         <v>9</v>
       </c>
       <c r="AQ49" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AR49" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AS49" t="s">
         <v>14</v>
       </c>
       <c r="AT49" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BH49" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -2478,7 +2508,7 @@
         <v>72</v>
       </c>
       <c r="C50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AJ50" t="s">
         <v>5</v>
@@ -2487,10 +2517,13 @@
         <v>9</v>
       </c>
       <c r="AR50" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AS50" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="AT50" t="s">
+        <v>15</v>
       </c>
       <c r="AU50" t="s">
         <v>14</v>
@@ -2505,10 +2538,10 @@
         <v>14</v>
       </c>
       <c r="AY50" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BI50" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="51">
@@ -2519,7 +2552,7 @@
         <v>76</v>
       </c>
       <c r="C51" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK51" t="s">
         <v>5</v>
@@ -2528,10 +2561,10 @@
         <v>9</v>
       </c>
       <c r="AS51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AT51" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AY51" t="s">
         <v>14</v>
@@ -2543,10 +2576,10 @@
         <v>14</v>
       </c>
       <c r="BB51" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BJ51" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
@@ -2557,7 +2590,7 @@
         <v>80</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AL52" t="s">
         <v>5</v>
@@ -2566,19 +2599,19 @@
         <v>9</v>
       </c>
       <c r="AT52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AU52" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BB52" t="s">
         <v>14</v>
       </c>
       <c r="BC52" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BK52" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -2589,7 +2622,7 @@
         <v>84</v>
       </c>
       <c r="C53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AN53" t="s">
         <v>5</v>
@@ -2598,19 +2631,19 @@
         <v>9</v>
       </c>
       <c r="AU53" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AV53" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AW53" t="s">
         <v>14</v>
       </c>
       <c r="AX53" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BL53" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
@@ -2621,7 +2654,7 @@
         <v>88</v>
       </c>
       <c r="C54" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AP54" t="s">
         <v>5</v>
@@ -2630,19 +2663,19 @@
         <v>9</v>
       </c>
       <c r="AV54" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AW54" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AX54" t="s">
         <v>14</v>
       </c>
       <c r="AY54" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BM54" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
@@ -2653,7 +2686,7 @@
         <v>68</v>
       </c>
       <c r="C55" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ55" t="s">
         <v>5</v>
@@ -2662,19 +2695,19 @@
         <v>9</v>
       </c>
       <c r="AW55" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AX55" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AY55" t="s">
         <v>14</v>
       </c>
       <c r="AZ55" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BN55" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
@@ -2685,7 +2718,7 @@
         <v>72</v>
       </c>
       <c r="C56" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ56" t="s">
         <v>5</v>
@@ -2694,10 +2727,10 @@
         <v>9</v>
       </c>
       <c r="AX56" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AY56" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="AZ56" t="s">
         <v>14</v>
@@ -2712,10 +2745,10 @@
         <v>14</v>
       </c>
       <c r="BD56" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BO56" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
@@ -2726,7 +2759,7 @@
         <v>76</v>
       </c>
       <c r="C57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AR57" t="s">
         <v>5</v>
@@ -2735,10 +2768,10 @@
         <v>9</v>
       </c>
       <c r="AY57" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="AZ57" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BD57" t="s">
         <v>14</v>
@@ -2750,10 +2783,10 @@
         <v>14</v>
       </c>
       <c r="BG57" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BP57" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
@@ -2764,7 +2797,7 @@
         <v>80</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR58" t="s">
         <v>5</v>
@@ -2773,19 +2806,19 @@
         <v>9</v>
       </c>
       <c r="AZ58" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BA58" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BG58" t="s">
         <v>14</v>
       </c>
       <c r="BH58" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ58" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
@@ -2796,7 +2829,7 @@
         <v>84</v>
       </c>
       <c r="C59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AT59" t="s">
         <v>5</v>
@@ -2805,19 +2838,19 @@
         <v>9</v>
       </c>
       <c r="BA59" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BB59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BC59" t="s">
         <v>14</v>
       </c>
       <c r="BD59" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BR59" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
@@ -2828,7 +2861,7 @@
         <v>88</v>
       </c>
       <c r="C60" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="AV60" t="s">
         <v>5</v>
@@ -2837,19 +2870,19 @@
         <v>9</v>
       </c>
       <c r="BB60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BC60" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BD60" t="s">
         <v>14</v>
       </c>
       <c r="BE60" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS60" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="61">
@@ -2860,7 +2893,7 @@
         <v>68</v>
       </c>
       <c r="C61" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW61" t="s">
         <v>5</v>
@@ -2869,19 +2902,19 @@
         <v>9</v>
       </c>
       <c r="BC61" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BD61" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BE61" t="s">
         <v>14</v>
       </c>
       <c r="BF61" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BT61" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="62">
@@ -2892,7 +2925,7 @@
         <v>72</v>
       </c>
       <c r="C62" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AW62" t="s">
         <v>5</v>
@@ -2901,10 +2934,10 @@
         <v>9</v>
       </c>
       <c r="BD62" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BE62" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BF62" t="s">
         <v>14</v>
@@ -2919,10 +2952,10 @@
         <v>14</v>
       </c>
       <c r="BJ62" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BU62" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="63">
@@ -2933,7 +2966,7 @@
         <v>76</v>
       </c>
       <c r="C63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AX63" t="s">
         <v>5</v>
@@ -2942,10 +2975,10 @@
         <v>9</v>
       </c>
       <c r="BE63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BF63" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BJ63" t="s">
         <v>14</v>
@@ -2957,10 +2990,10 @@
         <v>14</v>
       </c>
       <c r="BM63" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BV63" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="64">
@@ -2971,7 +3004,7 @@
         <v>80</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AX64" t="s">
         <v>5</v>
@@ -2980,19 +3013,19 @@
         <v>9</v>
       </c>
       <c r="BF64" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BG64" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BM64" t="s">
         <v>14</v>
       </c>
       <c r="BN64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BW64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="65">
@@ -3003,7 +3036,7 @@
         <v>84</v>
       </c>
       <c r="C65" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AZ65" t="s">
         <v>5</v>
@@ -3012,19 +3045,19 @@
         <v>9</v>
       </c>
       <c r="BG65" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BH65" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BI65" t="s">
         <v>14</v>
       </c>
       <c r="BJ65" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BX65" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="66">
@@ -3035,7 +3068,7 @@
         <v>88</v>
       </c>
       <c r="C66" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BA66" t="s">
         <v>5</v>
@@ -3044,19 +3077,19 @@
         <v>9</v>
       </c>
       <c r="BH66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BI66" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BJ66" t="s">
         <v>14</v>
       </c>
       <c r="BK66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BY66" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="67">
@@ -3067,7 +3100,7 @@
         <v>92</v>
       </c>
       <c r="C67" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="BK67" t="s">
         <v>5</v>
@@ -3085,10 +3118,10 @@
         <v>14</v>
       </c>
       <c r="BP67" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BZ67" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="68">
@@ -3099,7 +3132,7 @@
         <v>96</v>
       </c>
       <c r="C68" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="BK68" t="s">
         <v>5</v>
@@ -3108,7 +3141,7 @@
         <v>9</v>
       </c>
       <c r="BM68" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BP68" t="s">
         <v>14</v>
@@ -3120,10 +3153,10 @@
         <v>14</v>
       </c>
       <c r="BS68" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CA68" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="69">
@@ -3134,7 +3167,7 @@
         <v>100</v>
       </c>
       <c r="C69" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="BK69" t="s">
         <v>5</v>
@@ -3146,10 +3179,10 @@
         <v>14</v>
       </c>
       <c r="BN69" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CB69" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="70">
@@ -3160,7 +3193,7 @@
         <v>104</v>
       </c>
       <c r="C70" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="BK70" t="s">
         <v>5</v>
@@ -3172,10 +3205,10 @@
         <v>14</v>
       </c>
       <c r="BN70" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CC70" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="71">
@@ -3186,7 +3219,7 @@
         <v>36</v>
       </c>
       <c r="C71" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BL71" t="s">
         <v>5</v>
@@ -3204,10 +3237,10 @@
         <v>14</v>
       </c>
       <c r="BQ71" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CD71" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="72">
@@ -3218,7 +3251,7 @@
         <v>40</v>
       </c>
       <c r="C72" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BL72" t="s">
         <v>5</v>
@@ -3227,13 +3260,13 @@
         <v>9</v>
       </c>
       <c r="BN72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BO72" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BP72" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BQ72" t="s">
         <v>14</v>
@@ -3245,10 +3278,10 @@
         <v>14</v>
       </c>
       <c r="BT72" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CE72" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="73">
@@ -3259,7 +3292,7 @@
         <v>44</v>
       </c>
       <c r="C73" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BL73" t="s">
         <v>5</v>
@@ -3268,7 +3301,10 @@
         <v>9</v>
       </c>
       <c r="BP73" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="BT73" t="s">
+        <v>15</v>
       </c>
       <c r="BU73" t="s">
         <v>14</v>
@@ -3283,10 +3319,10 @@
         <v>14</v>
       </c>
       <c r="BY73" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CF73" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="74">
@@ -3297,7 +3333,7 @@
         <v>48</v>
       </c>
       <c r="C74" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BL74" t="s">
         <v>5</v>
@@ -3306,7 +3342,7 @@
         <v>9</v>
       </c>
       <c r="BP74" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BQ74" t="s">
         <v>14</v>
@@ -3321,10 +3357,10 @@
         <v>14</v>
       </c>
       <c r="BU74" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CG74" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="75">
@@ -3335,7 +3371,7 @@
         <v>52</v>
       </c>
       <c r="C75" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BM75" t="s">
         <v>5</v>
@@ -3344,7 +3380,7 @@
         <v>9</v>
       </c>
       <c r="BQ75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BR75" t="s">
         <v>14</v>
@@ -3365,10 +3401,10 @@
         <v>14</v>
       </c>
       <c r="BX75" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CH75" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="76">
@@ -3379,7 +3415,7 @@
         <v>56</v>
       </c>
       <c r="C76" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BM76" t="s">
         <v>5</v>
@@ -3388,16 +3424,16 @@
         <v>9</v>
       </c>
       <c r="BR76" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BS76" t="s">
         <v>14</v>
       </c>
       <c r="BT76" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CI76" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="77">
@@ -3417,16 +3453,16 @@
         <v>9</v>
       </c>
       <c r="BS77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BT77" t="s">
         <v>14</v>
       </c>
       <c r="BU77" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CJ77" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="78">
@@ -3437,7 +3473,7 @@
         <v>64</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BM78" t="s">
         <v>5</v>
@@ -3446,19 +3482,19 @@
         <v>9</v>
       </c>
       <c r="BT78" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BU78" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BV78" t="s">
         <v>14</v>
       </c>
       <c r="BW78" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CK78" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="79">
@@ -3469,7 +3505,7 @@
         <v>68</v>
       </c>
       <c r="C79" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BN79" t="s">
         <v>5</v>
@@ -3478,19 +3514,19 @@
         <v>9</v>
       </c>
       <c r="BU79" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BV79" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="BW79" t="s">
         <v>14</v>
       </c>
       <c r="BX79" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CL79" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="80">
@@ -3501,7 +3537,7 @@
         <v>72</v>
       </c>
       <c r="C80" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BN80" t="s">
         <v>5</v>
@@ -3510,10 +3546,13 @@
         <v>9</v>
       </c>
       <c r="BV80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BW80" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="BX80" t="s">
+        <v>15</v>
       </c>
       <c r="BY80" t="s">
         <v>14</v>
@@ -3528,10 +3567,10 @@
         <v>14</v>
       </c>
       <c r="CC80" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CM80" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="81">
@@ -3542,7 +3581,7 @@
         <v>76</v>
       </c>
       <c r="C81" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BO81" t="s">
         <v>5</v>
@@ -3551,10 +3590,10 @@
         <v>9</v>
       </c>
       <c r="BW81" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BX81" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CC81" t="s">
         <v>14</v>
@@ -3566,10 +3605,10 @@
         <v>14</v>
       </c>
       <c r="CF81" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CN81" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="82">
@@ -3580,7 +3619,7 @@
         <v>80</v>
       </c>
       <c r="C82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BP82" t="s">
         <v>5</v>
@@ -3589,19 +3628,19 @@
         <v>9</v>
       </c>
       <c r="BX82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BY82" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CF82" t="s">
         <v>14</v>
       </c>
       <c r="CG82" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CO82" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="83">
@@ -3612,7 +3651,7 @@
         <v>84</v>
       </c>
       <c r="C83" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BR83" t="s">
         <v>5</v>
@@ -3621,19 +3660,19 @@
         <v>9</v>
       </c>
       <c r="BY83" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="BZ83" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CA83" t="s">
         <v>14</v>
       </c>
       <c r="CB83" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CP83" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="84">
@@ -3644,7 +3683,7 @@
         <v>88</v>
       </c>
       <c r="C84" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BT84" t="s">
         <v>5</v>
@@ -3653,19 +3692,19 @@
         <v>9</v>
       </c>
       <c r="BZ84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CA84" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CB84" t="s">
         <v>14</v>
       </c>
       <c r="CC84" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CQ84" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="85">
@@ -3676,7 +3715,7 @@
         <v>68</v>
       </c>
       <c r="C85" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BU85" t="s">
         <v>5</v>
@@ -3685,19 +3724,19 @@
         <v>9</v>
       </c>
       <c r="CA85" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CB85" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CC85" t="s">
         <v>14</v>
       </c>
       <c r="CD85" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CR85" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="86">
@@ -3708,7 +3747,7 @@
         <v>72</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BU86" t="s">
         <v>5</v>
@@ -3717,10 +3756,10 @@
         <v>9</v>
       </c>
       <c r="CB86" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CC86" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CD86" t="s">
         <v>14</v>
@@ -3735,10 +3774,10 @@
         <v>14</v>
       </c>
       <c r="CH86" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CS86" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87">
@@ -3749,7 +3788,7 @@
         <v>76</v>
       </c>
       <c r="C87" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BV87" t="s">
         <v>5</v>
@@ -3758,10 +3797,10 @@
         <v>9</v>
       </c>
       <c r="CC87" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CD87" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CH87" t="s">
         <v>14</v>
@@ -3773,10 +3812,10 @@
         <v>14</v>
       </c>
       <c r="CK87" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CT87" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="88">
@@ -3787,7 +3826,7 @@
         <v>80</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BV88" t="s">
         <v>5</v>
@@ -3796,19 +3835,19 @@
         <v>9</v>
       </c>
       <c r="CD88" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CE88" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CK88" t="s">
         <v>14</v>
       </c>
       <c r="CL88" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CU88" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="89">
@@ -3819,7 +3858,7 @@
         <v>84</v>
       </c>
       <c r="C89" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="BX89" t="s">
         <v>5</v>
@@ -3828,19 +3867,19 @@
         <v>9</v>
       </c>
       <c r="CE89" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CF89" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CG89" t="s">
         <v>14</v>
       </c>
       <c r="CH89" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CV89" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="90">
@@ -3851,7 +3890,7 @@
         <v>88</v>
       </c>
       <c r="C90" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="BZ90" t="s">
         <v>5</v>
@@ -3860,19 +3899,19 @@
         <v>9</v>
       </c>
       <c r="CF90" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CG90" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CH90" t="s">
         <v>14</v>
       </c>
       <c r="CI90" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CW90" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91">
@@ -3883,7 +3922,7 @@
         <v>68</v>
       </c>
       <c r="C91" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="CA91" t="s">
         <v>5</v>
@@ -3892,19 +3931,19 @@
         <v>9</v>
       </c>
       <c r="CG91" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CH91" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CI91" t="s">
         <v>14</v>
       </c>
       <c r="CJ91" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CX91" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="92">
@@ -3915,7 +3954,7 @@
         <v>72</v>
       </c>
       <c r="C92" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="CA92" t="s">
         <v>5</v>
@@ -3924,10 +3963,10 @@
         <v>9</v>
       </c>
       <c r="CH92" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CI92" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CJ92" t="s">
         <v>14</v>
@@ -3942,10 +3981,10 @@
         <v>14</v>
       </c>
       <c r="CN92" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CY92" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="93">
@@ -3956,7 +3995,7 @@
         <v>76</v>
       </c>
       <c r="C93" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="CB93" t="s">
         <v>5</v>
@@ -3965,10 +4004,10 @@
         <v>9</v>
       </c>
       <c r="CI93" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CJ93" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CN93" t="s">
         <v>14</v>
@@ -3980,10 +4019,10 @@
         <v>14</v>
       </c>
       <c r="CQ93" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="CZ93" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="94">
@@ -3994,7 +4033,7 @@
         <v>80</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="CB94" t="s">
         <v>5</v>
@@ -4003,19 +4042,19 @@
         <v>9</v>
       </c>
       <c r="CJ94" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CK94" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CQ94" t="s">
         <v>14</v>
       </c>
       <c r="CR94" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DA94" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="95">
@@ -4026,7 +4065,7 @@
         <v>84</v>
       </c>
       <c r="C95" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="CD95" t="s">
         <v>5</v>
@@ -4035,19 +4074,19 @@
         <v>9</v>
       </c>
       <c r="CK95" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CL95" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CM95" t="s">
         <v>14</v>
       </c>
       <c r="CN95" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DB95" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="96">
@@ -4058,7 +4097,7 @@
         <v>88</v>
       </c>
       <c r="C96" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="CE96" t="s">
         <v>5</v>
@@ -4067,19 +4106,19 @@
         <v>9</v>
       </c>
       <c r="CL96" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CM96" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CN96" t="s">
         <v>14</v>
       </c>
       <c r="CO96" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DC96" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="97">
@@ -4090,7 +4129,7 @@
         <v>92</v>
       </c>
       <c r="C97" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="CO97" t="s">
         <v>5</v>
@@ -4108,10 +4147,10 @@
         <v>14</v>
       </c>
       <c r="CT97" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DD97" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="98">
@@ -4122,7 +4161,7 @@
         <v>96</v>
       </c>
       <c r="C98" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="CO98" t="s">
         <v>5</v>
@@ -4131,7 +4170,7 @@
         <v>9</v>
       </c>
       <c r="CQ98" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CT98" t="s">
         <v>14</v>
@@ -4143,10 +4182,10 @@
         <v>14</v>
       </c>
       <c r="CW98" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DE98" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="99">
@@ -4157,7 +4196,7 @@
         <v>100</v>
       </c>
       <c r="C99" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="CO99" t="s">
         <v>5</v>
@@ -4169,10 +4208,10 @@
         <v>14</v>
       </c>
       <c r="CR99" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DF99" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="100">
@@ -4183,7 +4222,7 @@
         <v>104</v>
       </c>
       <c r="C100" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="CO100" t="s">
         <v>5</v>
@@ -4192,10 +4231,10 @@
         <v>14</v>
       </c>
       <c r="CR100" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DG100" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="101">
@@ -4206,7 +4245,7 @@
         <v>108</v>
       </c>
       <c r="C101" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="CP101" t="s">
         <v>5</v>
@@ -4218,10 +4257,10 @@
         <v>14</v>
       </c>
       <c r="CS101" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DH101" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="102">
@@ -4232,7 +4271,7 @@
         <v>112</v>
       </c>
       <c r="C102" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="CP102" t="s">
         <v>5</v>
@@ -4241,16 +4280,16 @@
         <v>9</v>
       </c>
       <c r="CR102" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CS102" t="s">
         <v>14</v>
       </c>
       <c r="CT102" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DI102" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="103">
@@ -4261,7 +4300,7 @@
         <v>116</v>
       </c>
       <c r="C103" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="CP103" t="s">
         <v>5</v>
@@ -4270,16 +4309,16 @@
         <v>9</v>
       </c>
       <c r="CS103" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CT103" t="s">
         <v>14</v>
       </c>
       <c r="CU103" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DJ103" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="104">
@@ -4290,7 +4329,7 @@
         <v>120</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="CP104" t="s">
         <v>5</v>
@@ -4299,16 +4338,16 @@
         <v>9</v>
       </c>
       <c r="CT104" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CU104" t="s">
         <v>14</v>
       </c>
       <c r="CV104" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DK104" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="105">
@@ -4319,7 +4358,7 @@
         <v>124</v>
       </c>
       <c r="C105" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="CQ105" t="s">
         <v>5</v>
@@ -4328,16 +4367,16 @@
         <v>9</v>
       </c>
       <c r="CU105" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CV105" t="s">
         <v>14</v>
       </c>
       <c r="CW105" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DL105" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="106">
@@ -4348,7 +4387,7 @@
         <v>128</v>
       </c>
       <c r="C106" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="CQ106" t="s">
         <v>5</v>
@@ -4357,19 +4396,19 @@
         <v>9</v>
       </c>
       <c r="CV106" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CW106" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CX106" t="s">
         <v>14</v>
       </c>
       <c r="CY106" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DM106" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="107">
@@ -4380,7 +4419,7 @@
         <v>132</v>
       </c>
       <c r="C107" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="CQ107" t="s">
         <v>5</v>
@@ -4389,19 +4428,19 @@
         <v>9</v>
       </c>
       <c r="CW107" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="CX107" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="CY107" t="s">
         <v>14</v>
       </c>
       <c r="CZ107" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DN107" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="108">
@@ -4412,7 +4451,7 @@
         <v>136</v>
       </c>
       <c r="C108" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="CQ108" t="s">
         <v>5</v>
@@ -4421,19 +4460,19 @@
         <v>9</v>
       </c>
       <c r="CX108" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CY108" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="CZ108" t="s">
         <v>14</v>
       </c>
       <c r="DA108" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DO108" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109">
@@ -4444,7 +4483,7 @@
         <v>140</v>
       </c>
       <c r="C109" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="CR109" t="s">
         <v>5</v>
@@ -4453,24 +4492,24 @@
         <v>9</v>
       </c>
       <c r="CY109" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="CZ109" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="DA109" t="s">
         <v>14</v>
       </c>
       <c r="DB109" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="DP109" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="112">
@@ -4478,7 +4517,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="113">
@@ -4486,15 +4525,15 @@
         <v>9</v>
       </c>
       <c r="B113" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B114" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="115">
@@ -4502,39 +4541,55 @@
         <v>14</v>
       </c>
       <c r="B115" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B116" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B117" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
+        <v>34</v>
+      </c>
+      <c r="B119" t="s">
         <v>56</v>
       </c>
-      <c r="B119" t="s">
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
         <v>57</v>
+      </c>
+      <c r="B120" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
